--- a/marketing_report/outputs/Grado_Pregrado/Reporte_Asesores/17_reporte_asesores.xlsx
+++ b/marketing_report/outputs/Grado_Pregrado/Reporte_Asesores/17_reporte_asesores.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,6 +443,1466 @@
         <is>
           <t>Total_Inscriptos</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Contact Center</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>UCASAL Prod</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Fátima de los Ángeles Salvatierra Lopez</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Maria José Fernandez</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Florencia María Rosa Villarreal</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Rocio Belén Aguirre</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VERONICA PACHTMAN</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jennifer Marianela Saltos</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Melina Salvatierra</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ALEJO AGUSTIN BONARI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Camila Lamas Cil</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gimena Vallejos</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Jorge Ariel Cabaña</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Micaela Fabbron</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Francisco Gerardo Jover</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Andrea Eliana Lamas</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>VALERIA JESSICA PUIA</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Paula Luciana Martinez Rosas</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Camila Nahir Abraham Romano</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Romina Tamara Prado</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Daniel Luciano Chaile Soto</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fernanda Victoria Meza</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Camila Mendoza Klimasauskas</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>KAREN IRIS MAMANI</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Pablo Simon Soto</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Naomi Mailen Itati Cardozo</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Valentina Ariana Donat</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Neuquén Sede_30 NEUQUÉN</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Camila Gisela Pacheco</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Gabriela Cristina Aro Carrizo</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Dair Gabriela Lara García</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Romina Julieta Muratore</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Adolfo Alejandro Kugler Fernando</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Neuquén Sede_30</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chaco Resistencia</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>FORMOSA Sede_195</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Ana Sofía Gomez</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Carolina Eugenia Ferrer</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Claudia Ayelen Santana Alvarado</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Florencia Micaela Duran</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>VIRGINIA MARIA HUERGO CORNEJO</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Graciela Beatríz Sotelo</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Gral Roca Sede_168 GENERAL ROCA</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Aldana Rocío Bruno Blanco</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Aldana Rocio Bruno Blanco</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Rocío Belén Leiva</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Agostina Michaella Martinelli</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Manuel Altamirano</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Jazmin Giunta Katsini</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Chajarí Sede_31</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CONCORDIA Sede_192</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Fiamma Alejandra Spring</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Estefanía Pamela Quintana</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Ivanna Giselle Acosta</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CATAMARCA Sede_131</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BAHÍA BLANCA Sede_42</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>San Pedro - BsAs Sede_166</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Concordia Sede 192</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Villa Maria sede_14 VILLA MARÍA</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Aldana Micaela Quinteros</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>La Rioja Sede_28 LA RIOJA</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Posadas Sede_109 POSADAS</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Gualeguaychú Sede_198 GUALEGUAYCHÚ</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Venado Tuerto Sede_86 UAM VENADO TUERTO</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Ana Lia Gonzalez Albiol</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Quilmes Sede_89 UAM QUILMES</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Macarena De Singlau</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Junin Sede_87 UAM Junin</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Florencia SAN MARTÍN DE LOS AN</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>UAM Junin Sede_87</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Rosario Sede_62 ROSARIO</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Gladis Isabel Miranda</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Maria Victoria Isola</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>San Rafael Sede_145 SAN RAFAEL</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>María Belén Vazquez Rios</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Villa Maria Sede_14</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Bernardo de Irigoyen</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Gabriel Cortes</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Concep. Uruguay Sede_69</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Goya Sede_101 GOYA</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>San Vicente Sede_116 SAN VICENTE</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>San Vicente Sede_116</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>CUTRAL CO Sede_132</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>UAM VENADO TUERTO Sede_86</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Enzo Francisco Giannotti</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>San Rafael Sede_145</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Alicia Pernigotti</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Posadas Sede_109</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>GUALEGUAY</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>San Miguel Sede_33</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Victoria Sede_55 VICTORIA</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>CORRIENTES Sede_13</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Puerto Iguazú Sede_196 PUERTO IGUAZÚ</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Ibicuy Sede_75 IBICUY</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Santa Rosa Sede_138 SANTA ROSA</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Pehuajó Sede_159</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Santiago del Estero Sede_139 SANTIAGO DEL ESTERO</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Andrea Ferrer</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Victoria Sede_55</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>German Gutierrez</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Rosario Sede_62</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Carla Azcárate</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Santa Rosa Sede_138</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Ariana Guadalupe Fernandez</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Alberto Rivero Leandro N Alem Sede_163</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Zarate Sede_91 UAM ZARATE</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Burgos David Abel</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>junin Sede_60</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>María Lucia Carrer Torne</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Necochea Sede_147</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>R. Saenz Peña Sede_142 ROQUE SÁENZ PEÑA</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Puerto Iguazú Sede_196</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Necochea Sede_147 NECOCHEA</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Sergio Raúl Castillo</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Florencia Pozzo</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Mariela Yolanda Brito</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Oberá Sede_66 OBERÁ</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>UAM QUILMES Sede_89</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Roque Saenz Peña Sede_142</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Lujan Sede_180</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Zapala Sede_65 ZAPALA</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>DELEGACION ROQUE S PEÑA - CHACO</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Franco Gudiño Farfan</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Milagro Carecchio</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Rafael Roldan</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>María Florencia Carattoni</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Antonella Nahir Zenteno</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>NEUQUÉN - NEUQUEN</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Mar del Plata Cem Sede_76 Mar del Plata Cem</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>MARIA JOSE MARTINEZ FERRER</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Lourdes Valentina Speicher</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Avellaneda Sede_60</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Trenque Lauquen Sede_151 TRENQUE LAUQUEN</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>UAM ZARATE Sede_91</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Tucuman Sede_81</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Trenque Lauquen Sede_151</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Sofia Belén Luna Palopoli</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Santiago del Estero Sede_139</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Oberá Sede_66</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Paso de los Libres Sede_146 PASO DE LOS LIBRES</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Daniela Janet Osorio</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN NEUQUÉN - NEUQUEN</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>CAPIOVÍ Sede_51</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>RIO GALLEGOS - SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Rocío Belén Serrano</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -488,7 +1948,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>125241</v>
+        <v>125213</v>
       </c>
     </row>
     <row r="3">
@@ -518,7 +1978,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>51229</v>
+        <v>51213</v>
       </c>
     </row>
     <row r="5">
@@ -533,7 +1993,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>57339</v>
+        <v>57293</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +2038,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15522</v>
+        <v>15521</v>
       </c>
     </row>
     <row r="9">
@@ -698,7 +2158,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21746</v>
+        <v>21723</v>
       </c>
     </row>
     <row r="17">
@@ -2082,10 +3542,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7782</v>
+        <v>7790</v>
       </c>
       <c r="C2" t="n">
-        <v>81.7007874015748</v>
+        <v>81.78477690288713</v>
       </c>
     </row>
     <row r="3">
@@ -2095,10 +3555,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1348</v>
+        <v>1340</v>
       </c>
       <c r="C3" t="n">
-        <v>14.15223097112861</v>
+        <v>14.06824146981627</v>
       </c>
     </row>
     <row r="4">
@@ -2152,10 +3612,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>148930</v>
+        <v>148879</v>
       </c>
       <c r="C2" t="n">
-        <v>37.36739630064532</v>
+        <v>37.36528779596529</v>
       </c>
     </row>
     <row r="3">
@@ -2165,10 +3625,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>128567</v>
+        <v>128521</v>
       </c>
       <c r="C3" t="n">
-        <v>32.25820210961572</v>
+        <v>32.2558866786132</v>
       </c>
     </row>
     <row r="4">
@@ -2178,10 +3638,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>95744</v>
+        <v>95728</v>
       </c>
       <c r="C4" t="n">
-        <v>24.02272202651572</v>
+        <v>24.02557963266925</v>
       </c>
     </row>
     <row r="5">
@@ -2191,10 +3651,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24634</v>
+        <v>24633</v>
       </c>
       <c r="C5" t="n">
-        <v>6.18081273396963</v>
+        <v>6.182330176035658</v>
       </c>
     </row>
     <row r="6">
@@ -2207,7 +3667,7 @@
         <v>656</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1645941850078785</v>
+        <v>0.1646412777769412</v>
       </c>
     </row>
     <row r="7">
@@ -2220,7 +3680,7 @@
         <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004516303856923494</v>
+        <v>0.004517596036562411</v>
       </c>
     </row>
     <row r="8">
@@ -2233,7 +3693,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001756340388803581</v>
+        <v>0.001756842903107604</v>
       </c>
     </row>
   </sheetData>
